--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484635_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484635_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>12.5815</v>
+        <v>10.5838</v>
       </c>
       <c r="E2" t="n">
-        <v>9.8133</v>
+        <v>8.137600000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7682</v>
+        <v>2.4461</v>
       </c>
       <c r="G2" t="n">
         <v>8.5815</v>
@@ -610,13 +610,13 @@
         <v>4.0317</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7355</v>
+        <v>0.7377</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3424</v>
+        <v>0.6667</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3931</v>
+        <v>0.0711</v>
       </c>
       <c r="V2" t="n">
         <v>-0.9346</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4013</v>
+        <v>7.0085</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3329</v>
+        <v>2.9649</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0684</v>
+        <v>4.0436</v>
       </c>
       <c r="G3" t="n">
         <v>3.1893</v>
@@ -688,13 +688,13 @@
         <v>3.6651</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.1966</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6976</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1063</v>
+        <v>-0.1311</v>
       </c>
       <c r="V3" t="n">
         <v>1.267</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.515</v>
+        <v>2.3996</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8995</v>
+        <v>-0.9406</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4145</v>
+        <v>3.3402</v>
       </c>
       <c r="G4" t="n">
         <v>4.1691</v>
@@ -766,13 +766,13 @@
         <v>5.8642</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4342</v>
+        <v>-0.5496</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0521</v>
+        <v>0.011</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4862</v>
+        <v>-0.5606</v>
       </c>
       <c r="V4" t="n">
         <v>-2.5027</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3644</v>
+        <v>1.7346</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.7449</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3861</v>
+        <v>0.9897</v>
       </c>
       <c r="G5" t="n">
         <v>1.7953</v>
@@ -844,13 +844,13 @@
         <v>1.8326</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2863</v>
+        <v>-0.3435</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1847</v>
+        <v>-0.4182</v>
       </c>
       <c r="U5" t="n">
-        <v>0.471</v>
+        <v>0.0746</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6335</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2811</v>
+        <v>0.6745</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1868</v>
+        <v>-2.0906</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4679</v>
+        <v>2.7651</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6682</v>
@@ -922,13 +922,13 @@
         <v>3.1154</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2498</v>
+        <v>-0.8563</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3492</v>
+        <v>-0.253</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9006</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. CABRERA GONZALEZ</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4413</v>
+        <v>0.1705</v>
       </c>
       <c r="E7" t="n">
-        <v>0.115</v>
+        <v>-2.1377</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5563</v>
+        <v>2.3083</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1084</v>
+        <v>0.0419</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2781</v>
+        <v>-1.5029</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8303</v>
+        <v>1.5448</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4061</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6719000000000001</v>
+        <v>-0.2634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7342</v>
+        <v>0.1667</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2977</v>
+        <v>0.1386</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3938</v>
+        <v>-1.2395</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0961</v>
+        <v>1.3781</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.2828</v>
+        <v>2.7489</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>4.5814</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0551</v>
+        <v>-0.7198</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.092</v>
+        <v>-0.2085</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1471</v>
+        <v>-0.5113</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>-1.9005</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9554</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>S. CABRERA GONZALEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6244</v>
+        <v>-0.4413</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.5363</v>
+        <v>0.115</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9119</v>
+        <v>-0.5563</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0419</v>
+        <v>1.1084</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5029</v>
+        <v>0.2781</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5448</v>
+        <v>0.8303</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.09669999999999999</v>
+        <v>1.4061</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2634</v>
+        <v>0.6719000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1667</v>
+        <v>0.7342</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1386</v>
+        <v>-0.2977</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2395</v>
+        <v>-0.3938</v>
       </c>
       <c r="O8" t="n">
-        <v>1.3781</v>
+        <v>0.0961</v>
       </c>
       <c r="P8" t="n">
-        <v>2.7489</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>4.5814</v>
+        <v>0.5498</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5148</v>
+        <v>0.0551</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6071</v>
+        <v>-0.092</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9077</v>
+        <v>0.1471</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9005</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9005</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. MARI LOPEZ-ROCA</t>
+          <t>M. GONZALEZ BRU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0607</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5</v>
+        <v>-1.8349</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4393</v>
+        <v>1.3063</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1675</v>
+        <v>3.3739</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.214</v>
+        <v>-0.6844</v>
       </c>
       <c r="I9" t="n">
-        <v>2.3815</v>
+        <v>4.0583</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2368</v>
+        <v>2.9865</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1119</v>
+        <v>0.8512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8752</v>
+        <v>2.1352</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4042</v>
+        <v>0.3875</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1021</v>
+        <v>-1.5356</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5063</v>
+        <v>1.9231</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5498</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3823</v>
+        <v>3.1154</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1444</v>
+        <v>-1.1408</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7526</v>
+        <v>-0.5332</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3918</v>
+        <v>-0.6077</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6335</v>
+        <v>-2.212</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>-0.6231</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9554</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. GONZALEZ BRU</t>
+          <t>H. MARI LOPEZ-ROCA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.395</v>
+        <v>-0.9372</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3296</v>
+        <v>-2.2527</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9347</v>
+        <v>1.3155</v>
       </c>
       <c r="G10" t="n">
-        <v>3.3739</v>
+        <v>0.1675</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6844</v>
+        <v>-2.214</v>
       </c>
       <c r="I10" t="n">
-        <v>4.0583</v>
+        <v>2.3815</v>
       </c>
       <c r="J10" t="n">
-        <v>2.9865</v>
+        <v>-0.2368</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8512</v>
+        <v>-1.1119</v>
       </c>
       <c r="L10" t="n">
-        <v>2.1352</v>
+        <v>0.8752</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3875</v>
+        <v>0.4042</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5356</v>
+        <v>-1.1021</v>
       </c>
       <c r="O10" t="n">
-        <v>1.9231</v>
+        <v>1.5063</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1154</v>
+        <v>2.3823</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0072</v>
+        <v>-1.0209</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0279</v>
+        <v>-0.5053</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-0.5157</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.212</v>
+        <v>-0.6335</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6231</v>
+        <v>0.3219</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2115</v>
+        <v>-1.7034</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.5187</v>
+        <v>-3.8867</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3071</v>
+        <v>2.1833</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7232</v>
@@ -1312,13 +1312,13 @@
         <v>2.0158</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5041</v>
+        <v>0.004</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9909</v>
+        <v>-0.359</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4868</v>
+        <v>0.3629</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>18.4104</v>
+        <v>18.9609</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.731400000000001</v>
+        <v>-1.180799999999999</v>
       </c>
       <c r="F12" t="n">
         <v>20.1418</v>
@@ -1357,7 +1357,7 @@
         <v>18.0355</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.0377</v>
+        <v>-1.037699999999999</v>
       </c>
       <c r="I12" t="n">
         <v>19.0731</v>
@@ -1366,7 +1366,7 @@
         <v>15.672</v>
       </c>
       <c r="K12" t="n">
-        <v>7.815900000000001</v>
+        <v>7.815899999999999</v>
       </c>
       <c r="L12" t="n">
         <v>7.855899999999999</v>
@@ -1390,16 +1390,16 @@
         <v>31.1537</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.581500000000001</v>
+        <v>-4.0307</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.3075</v>
+        <v>-1.7571</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.2739</v>
+        <v>-2.274</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.871699999999999</v>
+        <v>-7.8717</v>
       </c>
       <c r="W12" t="n">
         <v>3.2298</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6596</v>
+        <v>3.4604</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7471</v>
+        <v>1.2663</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9125</v>
+        <v>2.1941</v>
       </c>
       <c r="G13" t="n">
         <v>0.2933</v>
@@ -1468,13 +1468,13 @@
         <v>2.1991</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9607</v>
+        <v>0.7615</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6026</v>
+        <v>0.1218</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3581</v>
+        <v>0.6397</v>
       </c>
       <c r="V13" t="n">
         <v>2.2224</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4755</v>
+        <v>0.2108</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.3472</v>
+        <v>-0.9626</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8717</v>
+        <v>1.1733</v>
       </c>
       <c r="G15" t="n">
         <v>-3.2533</v>
@@ -1624,13 +1624,13 @@
         <v>1.8326</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1156</v>
+        <v>0.8018</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.276</v>
+        <v>0.1086</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3916</v>
+        <v>0.6932</v>
       </c>
       <c r="V15" t="n">
         <v>2.8455</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7154</v>
+        <v>-0.3162</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7347</v>
+        <v>-0.5424</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0194</v>
+        <v>0.2262</v>
       </c>
       <c r="G16" t="n">
         <v>-2.9464</v>
@@ -1702,13 +1702,13 @@
         <v>1.8326</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3697</v>
+        <v>0.7689</v>
       </c>
       <c r="T16" t="n">
-        <v>0.31</v>
+        <v>0.5023</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0597</v>
+        <v>0.2666</v>
       </c>
       <c r="V16" t="n">
         <v>0.945</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8743</v>
+        <v>-0.9764</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3752</v>
+        <v>-0.2791</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4991</v>
+        <v>-0.6973</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8766</v>
@@ -1780,13 +1780,13 @@
         <v>0.733</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9131</v>
+        <v>0.8111</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.1686</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8407</v>
+        <v>0.6425</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6439</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>L. JURADO TRAVER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9907</v>
+        <v>-1.1704</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0375</v>
+        <v>-0.5092</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0469</v>
+        <v>-0.6611</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1582</v>
+        <v>-0.904</v>
       </c>
       <c r="H18" t="n">
-        <v>2.03</v>
+        <v>0.8269</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8719</v>
+        <v>-1.7309</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6147</v>
+        <v>-0.22</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8453</v>
+        <v>1.062</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2305</v>
+        <v>-1.2821</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4566</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8152</v>
+        <v>-0.2351</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6413</v>
+        <v>-0.4489</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.1312</v>
+        <v>0.3665</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.5135</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3823</v>
+        <v>0.3665</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5034</v>
+        <v>-0.3109</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6938</v>
+        <v>-0.2892</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1904</v>
+        <v>-0.0217</v>
       </c>
       <c r="V18" t="n">
-        <v>3.479</v>
+        <v>-0.3219</v>
       </c>
       <c r="W18" t="n">
-        <v>3.1674</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3115</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. JURADO TRAVER</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1427</v>
+        <v>-1.3155</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6054</v>
+        <v>-2.6145</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5373</v>
+        <v>1.2989</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.904</v>
+        <v>0.1582</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8269</v>
+        <v>2.03</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7309</v>
+        <v>-1.8719</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.22</v>
+        <v>1.6147</v>
       </c>
       <c r="K19" t="n">
-        <v>1.062</v>
+        <v>2.8453</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2821</v>
+        <v>-1.2305</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-1.4566</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2351</v>
+        <v>-0.8152</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4489</v>
+        <v>-0.6413</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3665</v>
+        <v>-5.1312</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-7.5135</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3665</v>
+        <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2832</v>
+        <v>0.1785</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3854</v>
+        <v>0.1169</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1022</v>
+        <v>0.0616</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3219</v>
+        <v>3.479</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.1674</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3219</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3936</v>
+        <v>-2.0031</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9169</v>
+        <v>-1.7246</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4766</v>
+        <v>-0.2784</v>
       </c>
       <c r="G20" t="n">
         <v>0.1138</v>
@@ -2014,13 +2014,13 @@
         <v>0.9163</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6748</v>
+        <v>-0.2843</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2941</v>
+        <v>-0.1018</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3807</v>
+        <v>-0.1825</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8118</v>
+        <v>-2.0367</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1206</v>
+        <v>-2.5437</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3089</v>
+        <v>0.507</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6431</v>
@@ -2092,13 +2092,13 @@
         <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5639999999999999</v>
+        <v>0.2112</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6063</v>
+        <v>-0.0294</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0424</v>
+        <v>0.2405</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3219</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3775</v>
+        <v>-4.6442</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9713</v>
+        <v>-5.1479</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4062</v>
+        <v>0.5037</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.2355</v>
+        <v>-3.1113</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.3411</v>
+        <v>-1.5499</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1056</v>
+        <v>-1.5613</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.773</v>
+        <v>-0.9586</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8147</v>
+        <v>-0.3593</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0417</v>
+        <v>-0.5994</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4624</v>
+        <v>-2.1526</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.5264</v>
+        <v>-1.1907</v>
       </c>
       <c r="O22" t="n">
-        <v>0.064</v>
+        <v>-0.962</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.4819</v>
+        <v>-2.1991</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5814</v>
+        <v>-4.7647</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0995</v>
+        <v>2.5656</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0729</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1162</v>
+        <v>0.5754</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0433</v>
+        <v>0.4231</v>
       </c>
       <c r="V22" t="n">
-        <v>1.267</v>
+        <v>-0.3324</v>
       </c>
       <c r="W22" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8882</v>
+        <v>-4.6951</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3304</v>
+        <v>-4.6444</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5578</v>
+        <v>-0.0507</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.906</v>
+        <v>-3.2355</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.236</v>
+        <v>-3.3411</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.67</v>
+        <v>0.1056</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6238</v>
+        <v>-1.773</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.0502</v>
+        <v>-1.8147</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5736</v>
+        <v>0.0417</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.2822</v>
+        <v>-1.4624</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.1858</v>
+        <v>-1.5264</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0964</v>
+        <v>0.064</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9163</v>
+        <v>-3.4819</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-4.5814</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2011</v>
+        <v>0.7553</v>
       </c>
       <c r="T23" t="n">
-        <v>1.0423</v>
+        <v>0.4431</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1588</v>
+        <v>0.3122</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.267</v>
+        <v>1.267</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.6757</v>
+        <v>-4.9173</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.7248</v>
+        <v>-3.715</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0491</v>
+        <v>-1.2023</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1113</v>
+        <v>-3.906</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5499</v>
+        <v>-3.236</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5613</v>
+        <v>-0.67</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9586</v>
+        <v>-1.6238</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.3593</v>
+        <v>-1.0502</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5994</v>
+        <v>-0.5736</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1526</v>
+        <v>-2.2822</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1907</v>
+        <v>-2.1858</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.962</v>
+        <v>-0.0964</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.1991</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7647</v>
+        <v>-2.7489</v>
       </c>
       <c r="R24" t="n">
-        <v>2.5656</v>
+        <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.033</v>
+        <v>1.172</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0015</v>
+        <v>0.6576</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0315</v>
+        <v>0.5143</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3324</v>
+        <v>-1.267</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3324</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.4105</v>
+        <v>-17.1284</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.1416</v>
+        <v>-20.1418</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7315</v>
+        <v>3.0134</v>
       </c>
       <c r="G25" t="n">
         <v>-18.0356</v>
@@ -2392,7 +2392,7 @@
         <v>-7.815799999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.856000000000001</v>
+        <v>-7.856</v>
       </c>
       <c r="P25" t="n">
         <v>-12.8281</v>
@@ -2404,13 +2404,13 @@
         <v>18.3257</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5815</v>
+        <v>5.863599999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>2.274</v>
+        <v>2.2739</v>
       </c>
       <c r="U25" t="n">
-        <v>2.3076</v>
+        <v>3.589499999999999</v>
       </c>
       <c r="V25" t="n">
         <v>7.8718</v>
